--- a/Digital-Business-Toolkit/06-Labor/Product.xlsx
+++ b/Digital-Business-Toolkit/06-Labor/Product.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Main Workspace" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Quick Start" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="User Guide" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="לוח בקרה" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="שולחן עבודה" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="התחלה מהירה" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="מדריך שימוש" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -660,7 +660,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Employee &amp; Labor Cost Tracker — Dashboard</t>
+          <t>לוח בקרה — מעקב שעות ועלות עובדים</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -671,7 +671,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — Know your true labor cost, every day</t>
+          <t>ContractorOS — דעו את עלות העבודה האמיתית שלכם, כל יום</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -708,42 +708,42 @@
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="B6" s="6">
-        <f>SUM('Main Workspace'!F4:F38)+SUM('Main Workspace'!G4:G38)</f>
+        <f>SUM('שולחן עבודה'!F4:F38)+SUM('שולחן עבודה'!G4:G38)</f>
         <v/>
       </c>
       <c r="C6" s="7">
-        <f>SUM('Main Workspace'!J4:J38)</f>
+        <f>SUM('שולחן עבודה'!J4:J38)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>SUM('Main Workspace'!G4:G38)</f>
+        <f>SUM('שולחן עבודה'!G4:G38)</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>IFERROR(SUM('Main Workspace'!J4:J38)/(SUM('Main Workspace'!F4:F38)+SUM('Main Workspace'!G4:G38)),0)</f>
+        <f>IFERROR(SUM('שולחן עבודה'!J4:J38)/(SUM('שולחן עבודה'!F4:F38)+SUM('שולחן עבודה'!G4:G38)),0)</f>
         <v/>
       </c>
       <c r="F6" s="8">
-        <f>COUNTA('Main Workspace'!B4:B38)</f>
+        <f>COUNTA('שולחן עבודה'!B4:B38)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>⚠ Business Insights / התראות</t>
+          <t>⚠ תובנות עסקיות והתראות</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="10">
-        <f>IF(SUM('Main Workspace'!G4:G38)&gt;20,"סך שעות נוספות גבוה החודש — בדקו עומס עבודה.","שעות נוספות בטווח סביר.")</f>
+        <f>IF(SUM('שולחן עבודה'!G4:G38)&gt;20,"סך שעות נוספות גבוה החודש — בדקו עומס עבודה.","שעות נוספות בטווח סביר.")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="11">
-        <f>IF(COUNTA('Main Workspace'!B4:B38)=0,"עדיין לא הוזנו נתוני שעות.","נתוני השעות מתעדכנים אוטומטית מהלשונית Main Workspace.")</f>
+        <f>IF(COUNTA('שולחן עבודה'!B4:B38)=0,"עדיין לא הוזנו נתוני שעות.","נתוני השעות מתעדכנים אוטומטית מהלשונית שולחן עבודה.")</f>
         <v/>
       </c>
     </row>
@@ -785,7 +785,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>מעקב שעות ועלות עובדים | Employee &amp; Labor Cost Tracker</t>
+          <t>מעקב שעות ועלות עובדים</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -884,7 +884,7 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>PRJ-0001</t>
+          <t>שיפוץ מטבח - וילה כהן</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>PRJ-0001</t>
+          <t>שיפוץ מטבח - וילה כהן</t>
         </is>
       </c>
       <c r="D5" s="16" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>PRJ-0002</t>
+          <t>החלפת לוח חשמל</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>PRJ-0001</t>
+          <t>שיפוץ מטבח - וילה כהן</t>
         </is>
       </c>
       <c r="D7" s="16" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>PRJ-0002</t>
+          <t>החלפת לוח חשמל</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
@@ -1767,7 +1767,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>התחלה מהירה | Quick Start</t>
+          <t>התחלה מהירה</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1783,7 +1783,7 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="29" t="inlineStr">
         <is>
-          <t>1. עברו ללשונית 'Main Workspace'.</t>
+          <t>1. עברו ללשונית 'שולחן עבודה'.</t>
         </is>
       </c>
     </row>
@@ -1811,14 +1811,14 @@
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>5. עברו ל-Dashboard לראות סה"כ שעות, עלות עבודה כוללת ושעות נוספות.</t>
+          <t>5. עברו ל-לוח הבקרה לראות סה"כ שעות, עלות עבודה כוללת ושעות נוספות.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>טיפ: השתמשו באותו מספר פרויקט (PRJ-XXXX) שבו אתם משתמשים בשאר הכלים, כדי שהעלות תתחבר נכון לכל פרויקט.</t>
+          <t>טיפ: השתמשו באותו שם פרויקט (בדיוק כפי שהוא מופיע במוצרים האחרים), כדי שהעלות תתחבר נכון לכל פרויקט.</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>מדריך שימוש | User Guide</t>
+          <t>מדריך שימוש</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1945,7 +1945,7 @@
     <row r="10" ht="46" customHeight="1">
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>מה Dashboard מציג?</t>
+          <t>מה לוח הבקרה מציג?</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -1969,7 +1969,7 @@
     <row r="13">
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>שאלות נפוצות (FAQ)</t>
+          <t>שאלות נפוצות</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
-          <t>כן — סננו את הטבלה לפי מספר פרויקט, או השתמשו ב-SUMIF על עמודת 'עלות יומית'.</t>
+          <t>כן — סננו את הטבלה לפי שם פרויקט, או השתמשו ב-SUMIF על עמודת 'עלות יומית'.</t>
         </is>
       </c>
     </row>

--- a/Digital-Business-Toolkit/06-Labor/Product.xlsx
+++ b/Digital-Business-Toolkit/06-Labor/Product.xlsx
@@ -671,7 +671,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — דעו את עלות העבודה האמיתית שלכם, כל יום</t>
+          <t>JobMargin — דעו את עלות העבודה האמיתית שלכם, כל יום</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
